--- a/jira_export_2026-10-22.xlsx
+++ b/jira_export_2026-10-22.xlsx
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -14472,7 +14472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14496,7 +14496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 17 commande(s)</t>
+          <t>Épics créées ce mois — 18 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14596,22 +14596,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36474</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36465</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -14631,32 +14631,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00185032</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>2500</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36459</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36453</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t xml:space="preserve">COMMUNE DE EVREUX </t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14676,32 +14676,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00184982</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>985</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36335</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -14721,32 +14721,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00184406</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36349</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36345</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LEUCATE Service Achat</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14766,32 +14766,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00184482</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36376</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36370</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -14811,11 +14811,11 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00184665</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -14911,22 +14911,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36459</t>
+          <t>PDMDEP-36376</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36453</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE EVREUX </t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -14946,32 +14946,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00184982</t>
+          <t>00184665</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36474</t>
+          <t>PDMDEP-36349</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36465</t>
+          <t>PDMDEP-36345</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>MAIRIE DE LEUCATE Service Achat</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -14991,32 +14991,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00185032</t>
+          <t>00184482</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>4685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36427</t>
+          <t>PDMDEP-36555</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36549</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -15036,32 +15036,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00184846</t>
+          <t>00185556</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>3575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36428</t>
+          <t>PDMDEP-36197</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36190</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00184334</t>
+          <t>00183894</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36439</t>
+          <t>PDMDEP-36402</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36435</t>
+          <t>PDMDEP-36398</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANGERS</t>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -15126,32 +15126,32 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00184863</t>
+          <t>00184748</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36497</t>
+          <t>PDMDEP-36428</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36493</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE SEINE ET MARNE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00185186</t>
+          <t>00184334</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
@@ -15181,22 +15181,22 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -15216,32 +15216,32 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>5718</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36402</t>
+          <t>PDMDEP-36497</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36398</t>
+          <t>PDMDEP-36493</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+          <t>DEPARTEMENT DE SEINE ET MARNE</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00184748</t>
+          <t>00185186</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
@@ -15271,73 +15271,97 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-36427</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36421</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>00184846</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I22" s="26" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>17 commande(s)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>26968</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" s="17" t="n"/>
@@ -15348,17 +15372,17 @@
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>7 commande(s)</t>
+          <t>18 commande(s)</t>
         </is>
       </c>
       <c r="I23" s="24" t="n">
-        <v>15603</v>
+        <v>26968</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B24" s="17" t="n"/>
@@ -15369,10 +15393,31 @@
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>15603</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
           <t>10 commande(s)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="n">
+      <c r="I25" s="24" t="n">
         <v>11365</v>
       </c>
     </row>
